--- a/wk3/more_formulas_Excel_Tutorial.xlsx
+++ b/wk3/more_formulas_Excel_Tutorial.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop W11\working_folder\Personales\Upright\Data_Science\instructor-dab-sep-2026\wk3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D4D720-E9C4-4A56-AC90-F53B642B78F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A2CC19-B2F5-4F0F-96DA-7CE700D82FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.PEMDAS" sheetId="9" r:id="rId1"/>
@@ -2465,7 +2465,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> Calculating totals across a list (Price $\times$ Quantity).</a:t>
+            <a:t> Calculating totals across a list (Price x Quantity).</a:t>
           </a:r>
         </a:p>
         <a:p>
